--- a/documentation/Product Data Reference.xlsx
+++ b/documentation/Product Data Reference.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StevenUsher\Documents\Programming Projects\Shipping Estimator\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1974AEAD-0E2B-4EF3-9012-C89500B7BEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBAA2BE-4336-4941-A0C2-DAF31382CE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -670,10 +670,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -682,6 +678,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -996,7 +996,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -1010,32 +1010,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="21"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
     </row>
     <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -1074,16 +1074,16 @@
       <c r="A4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
     </row>
     <row r="5" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -1423,16 +1423,16 @@
       <c r="A20" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
     </row>
     <row r="21" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
@@ -1698,16 +1698,16 @@
       <c r="A34" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
     </row>
     <row r="35" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -1893,16 +1893,16 @@
       <c r="A45" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
     </row>
     <row r="46" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
@@ -1911,14 +1911,14 @@
       <c r="B46" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E46" s="17"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="19"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="17"/>
       <c r="K46" s="12" t="s">
         <v>69</v>
       </c>
@@ -1930,14 +1930,14 @@
       <c r="B47" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E47" s="17"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="19"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
+      <c r="H47" s="16"/>
+      <c r="I47" s="17"/>
       <c r="K47" s="12" t="s">
         <v>71</v>
       </c>
@@ -1949,14 +1949,14 @@
       <c r="B48" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D48" s="16" t="s">
+      <c r="D48" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="E48" s="17"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="19"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="17"/>
       <c r="K48" s="12" t="s">
         <v>74</v>
       </c>
@@ -1968,14 +1968,14 @@
       <c r="B49" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="D49" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E49" s="17"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="18"/>
-      <c r="I49" s="19"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="17"/>
       <c r="K49" s="12" t="s">
         <v>77</v>
       </c>
@@ -1987,12 +1987,12 @@
       <c r="B50" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D50" s="16"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="18"/>
-      <c r="I50" s="19"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="16"/>
+      <c r="I50" s="17"/>
       <c r="K50" s="12"/>
     </row>
     <row r="51" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2002,14 +2002,14 @@
       <c r="B51" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D51" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="E51" s="17"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="18"/>
-      <c r="I51" s="19"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="17"/>
       <c r="K51" s="12" t="s">
         <v>77</v>
       </c>
@@ -2021,12 +2021,12 @@
       <c r="B52" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D52" s="16"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="18"/>
-      <c r="G52" s="18"/>
-      <c r="H52" s="18"/>
-      <c r="I52" s="19"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="17"/>
       <c r="K52" s="12"/>
     </row>
     <row r="53" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2036,14 +2036,14 @@
       <c r="B53" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D53" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="E53" s="17"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="19"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="17"/>
       <c r="K53" s="12" t="s">
         <v>77</v>
       </c>
@@ -2055,12 +2055,12 @@
       <c r="B54" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D54" s="16"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="18"/>
-      <c r="I54" s="19"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="17"/>
       <c r="K54" s="12"/>
     </row>
     <row r="55" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2070,14 +2070,14 @@
       <c r="B55" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D55" s="16" t="s">
+      <c r="D55" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="E55" s="17"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="18"/>
-      <c r="I55" s="19"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="16"/>
+      <c r="I55" s="17"/>
       <c r="K55" s="12" t="s">
         <v>84</v>
       </c>
@@ -2089,14 +2089,14 @@
       <c r="B56" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D56" s="16" t="s">
+      <c r="D56" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E56" s="17"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="19"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="16"/>
+      <c r="H56" s="16"/>
+      <c r="I56" s="17"/>
       <c r="K56" s="12" t="s">
         <v>87</v>
       </c>
@@ -2106,23 +2106,24 @@
         <v>127</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>140</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="D52:I52"/>
     <mergeCell ref="D50:I50"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="D56:I56"/>
@@ -2139,7 +2140,6 @@
     <mergeCell ref="D55:I55"/>
     <mergeCell ref="D53:I53"/>
     <mergeCell ref="D54:I54"/>
-    <mergeCell ref="D52:I52"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="54" fitToHeight="0" orientation="landscape" r:id="rId1"/>
